--- a/diseases/d236/2010-2014.xlsx
+++ b/diseases/d236/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>35</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>11.00082349021555</v>
       </c>
@@ -1410,9 +1407,6 @@
       <c r="O5" t="n">
         <v>77</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.574912019687627</v>
       </c>
@@ -1806,9 +1800,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>1.227204171185164</v>
       </c>
@@ -2202,9 +2193,6 @@
       <c r="O9" t="n">
         <v>69</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>1.411284796862939</v>
       </c>
@@ -2598,9 +2586,6 @@
       <c r="O11" t="n">
         <v>65</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>1.329471185450595</v>
       </c>
@@ -2994,9 +2979,6 @@
       <c r="O13" t="n">
         <v>59</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.206750768332078</v>
       </c>
@@ -3390,9 +3372,6 @@
       <c r="O15" t="n">
         <v>78</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>1.595365422540714</v>
       </c>
@@ -3786,9 +3765,6 @@
       <c r="O17" t="n">
         <v>63</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>1.288564379744422</v>
       </c>
@@ -4182,9 +4158,6 @@
       <c r="O19" t="n">
         <v>132</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>2.699849176607362</v>
       </c>
@@ -4578,9 +4551,6 @@
       <c r="O21" t="n">
         <v>85</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>1.738539242512316</v>
       </c>
@@ -4974,9 +4944,6 @@
       <c r="O23" t="n">
         <v>81</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.656725631099972</v>
       </c>
@@ -5370,9 +5337,6 @@
       <c r="O25" t="n">
         <v>81</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>1.656725631099972</v>
       </c>
@@ -5766,9 +5730,6 @@
       <c r="O27" t="n">
         <v>59</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>1.206750768332078</v>
       </c>
@@ -6162,9 +6123,6 @@
       <c r="O29" t="n">
         <v>58</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>18.17401304142108</v>
       </c>
@@ -6807,9 +6765,6 @@
       <c r="O32" t="n">
         <v>102</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>2.059371269913313</v>
       </c>
@@ -7203,9 +7158,6 @@
       <c r="O34" t="n">
         <v>74</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>1.494053666407697</v>
       </c>
@@ -7599,9 +7551,6 @@
       <c r="O36" t="n">
         <v>87</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>1.75652255374959</v>
       </c>
@@ -7995,9 +7944,6 @@
       <c r="O38" t="n">
         <v>55</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>1.110445292600316</v>
       </c>
@@ -8391,9 +8337,6 @@
       <c r="O40" t="n">
         <v>79</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>1.595003238462271</v>
       </c>
@@ -8787,9 +8730,6 @@
       <c r="O42" t="n">
         <v>88</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>1.776712468160505</v>
       </c>
@@ -9183,9 +9123,6 @@
       <c r="O44" t="n">
         <v>80</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>1.615193152873186</v>
       </c>
@@ -9579,9 +9516,6 @@
       <c r="O46" t="n">
         <v>116</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>2.34203007166612</v>
       </c>
@@ -9975,9 +9909,6 @@
       <c r="O48" t="n">
         <v>117</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>2.362219986077035</v>
       </c>
@@ -10371,9 +10302,6 @@
       <c r="O50" t="n">
         <v>90</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>1.817092296982334</v>
       </c>
@@ -10767,9 +10695,6 @@
       <c r="O52" t="n">
         <v>87</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.75652255374959</v>
       </c>
@@ -11163,9 +11088,6 @@
       <c r="O54" t="n">
         <v>85</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>1.71614272492776</v>
       </c>
@@ -11559,9 +11481,6 @@
       <c r="O56" t="n">
         <v>41</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>12.7789353276784</v>
       </c>
@@ -12204,9 +12123,6 @@
       <c r="O59" t="n">
         <v>86</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>1.713673972530404</v>
       </c>
@@ -12600,9 +12516,6 @@
       <c r="O61" t="n">
         <v>80</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>1.594115323284097</v>
       </c>
@@ -12996,9 +12909,6 @@
       <c r="O63" t="n">
         <v>95</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.893011946399865</v>
       </c>
@@ -13392,9 +13302,6 @@
       <c r="O65" t="n">
         <v>64</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>1.275292258627277</v>
       </c>
@@ -13788,9 +13695,6 @@
       <c r="O67" t="n">
         <v>79</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>1.574188881743046</v>
       </c>
@@ -14184,9 +14088,6 @@
       <c r="O69" t="n">
         <v>117</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>2.331393660302991</v>
       </c>
@@ -14580,9 +14481,6 @@
       <c r="O71" t="n">
         <v>111</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>2.211835011056684</v>
       </c>
@@ -14976,9 +14874,6 @@
       <c r="O73" t="n">
         <v>161</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>3.208157088109245</v>
       </c>
@@ -15372,9 +15267,6 @@
       <c r="O75" t="n">
         <v>115</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>2.291540777220889</v>
       </c>
@@ -15768,9 +15660,6 @@
       <c r="O77" t="n">
         <v>100</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>1.992644154105121</v>
       </c>
@@ -16164,9 +16053,6 @@
       <c r="O79" t="n">
         <v>111</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>2.211835011056684</v>
       </c>
@@ -16560,9 +16446,6 @@
       <c r="O81" t="n">
         <v>85</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>1.693747530989353</v>
       </c>
@@ -16956,9 +16839,6 @@
       <c r="O83" t="n">
         <v>32</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>9.880034765372331</v>
       </c>
@@ -17601,9 +17481,6 @@
       <c r="O86" t="n">
         <v>116</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>2.283408605438705</v>
       </c>
@@ -17997,9 +17874,6 @@
       <c r="O88" t="n">
         <v>87</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>1.712556454079029</v>
       </c>
@@ -18393,9 +18267,6 @@
       <c r="O90" t="n">
         <v>109</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>2.145616706834645</v>
       </c>
@@ -18789,9 +18660,6 @@
       <c r="O92" t="n">
         <v>108</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>2.125932149891208</v>
       </c>
@@ -19185,9 +19053,6 @@
       <c r="O94" t="n">
         <v>126</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>2.480254174873076</v>
       </c>
@@ -19581,9 +19446,6 @@
       <c r="O96" t="n">
         <v>110</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>2.165301263778083</v>
       </c>
@@ -19977,9 +19839,6 @@
       <c r="O98" t="n">
         <v>119</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>2.342462276269017</v>
       </c>
@@ -20373,9 +20232,6 @@
       <c r="O100" t="n">
         <v>156</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>3.07079088317619</v>
       </c>
@@ -20769,9 +20625,6 @@
       <c r="O102" t="n">
         <v>167</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>3.287321009553998</v>
       </c>
@@ -21165,9 +21018,6 @@
       <c r="O104" t="n">
         <v>153</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>3.011737212345879</v>
       </c>
@@ -21561,9 +21411,6 @@
       <c r="O106" t="n">
         <v>117</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>2.303093162382142</v>
       </c>
@@ -21957,9 +21804,6 @@
       <c r="O108" t="n">
         <v>115</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>2.263724048495268</v>
       </c>
@@ -22353,9 +22197,6 @@
       <c r="O110" t="n">
         <v>55</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>16.79325216594786</v>
       </c>
@@ -22998,9 +22839,6 @@
       <c r="O113" t="n">
         <v>117</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>2.277418808559591</v>
       </c>
@@ -23394,9 +23232,6 @@
       <c r="O115" t="n">
         <v>118</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>2.296883926581468</v>
       </c>
@@ -23790,9 +23625,6 @@
       <c r="O117" t="n">
         <v>132</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>2.569395578887744</v>
       </c>
@@ -24186,9 +24018,6 @@
       <c r="O119" t="n">
         <v>124</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>2.413674634712729</v>
       </c>
@@ -24582,9 +24411,6 @@
       <c r="O121" t="n">
         <v>160</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>3.114418883500295</v>
       </c>
@@ -24978,9 +24804,6 @@
       <c r="O123" t="n">
         <v>172</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>3.348000299762818</v>
       </c>
@@ -25374,9 +25197,6 @@
       <c r="O125" t="n">
         <v>157</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>3.056023529434665</v>
       </c>
@@ -25770,9 +25590,6 @@
       <c r="O127" t="n">
         <v>232</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>4.515907381075428</v>
       </c>
@@ -26166,9 +25983,6 @@
       <c r="O129" t="n">
         <v>226</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>4.399116672944167</v>
       </c>
@@ -26562,9 +26376,6 @@
       <c r="O131" t="n">
         <v>165</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>3.21174447360968</v>
       </c>
@@ -26958,9 +26769,6 @@
       <c r="O133" t="n">
         <v>127</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>2.472069988778359</v>
       </c>
@@ -27353,9 +27161,6 @@
       </c>
       <c r="O135" t="n">
         <v>137</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>2.666721168997128</v>
